--- a/Zeitplan.xlsx
+++ b/Zeitplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kotrnmr\Documents\BFS_2023-2026\LFA10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\W13116\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C66C17A-B6EE-4DF4-A21B-F251DAF4E38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C2B520-219F-43BE-94F7-091C7273751B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B5AE3885-56EE-4E2C-9945-187B43DC15E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B5AE3885-56EE-4E2C-9945-187B43DC15E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Phase</t>
   </si>
@@ -54,57 +51,21 @@
     <t>Projektstart &amp; Planung</t>
   </si>
   <si>
-    <t>Thema festlegen, GitHub, Umgebung</t>
-  </si>
-  <si>
-    <t>4 h</t>
-  </si>
-  <si>
     <t>Analyse</t>
   </si>
   <si>
-    <t>Stakeholder, Use Cases, Anforderungen</t>
-  </si>
-  <si>
-    <t>8 h</t>
-  </si>
-  <si>
     <t>Entwurf</t>
   </si>
   <si>
-    <t>Wireframes, UML, DB-Entwurf</t>
-  </si>
-  <si>
-    <t>12 h</t>
-  </si>
-  <si>
     <t>Implementierung</t>
   </si>
   <si>
-    <t>Anwendung + DB + Logik</t>
-  </si>
-  <si>
-    <t>28 h</t>
-  </si>
-  <si>
     <t>Tests &amp; Feedback</t>
   </si>
   <si>
-    <t>Fremdtest + eigener Test</t>
-  </si>
-  <si>
-    <t>6 h</t>
-  </si>
-  <si>
-    <t>laufend + Abschluss</t>
-  </si>
-  <si>
     <t>Präsentationsvorbereitung</t>
   </si>
   <si>
-    <t>Demo, Folien</t>
-  </si>
-  <si>
     <t>Puffer</t>
   </si>
   <si>
@@ -112,6 +73,81 @@
   </si>
   <si>
     <t>≈8 h</t>
+  </si>
+  <si>
+    <t>Thema festlegen</t>
+  </si>
+  <si>
+    <t>Github projekt anlegen</t>
+  </si>
+  <si>
+    <t>umgebung anlegen</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>Anforderungen</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>Use cases</t>
+  </si>
+  <si>
+    <t>6h</t>
+  </si>
+  <si>
+    <t>Stakeholder</t>
+  </si>
+  <si>
+    <t>UML</t>
+  </si>
+  <si>
+    <t>DB-Entwrf</t>
+  </si>
+  <si>
+    <t>Wireframes</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>Logik</t>
+  </si>
+  <si>
+    <t>12h</t>
+  </si>
+  <si>
+    <t>10h</t>
+  </si>
+  <si>
+    <t>Anwendung</t>
+  </si>
+  <si>
+    <t>eigener test</t>
+  </si>
+  <si>
+    <t>4h</t>
+  </si>
+  <si>
+    <t>Fremdtest</t>
+  </si>
+  <si>
+    <t>Abschluss</t>
+  </si>
+  <si>
+    <t>laufend</t>
+  </si>
+  <si>
+    <t>Folien</t>
+  </si>
+  <si>
+    <t>Demo</t>
   </si>
 </sst>
 </file>
@@ -143,7 +179,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -209,26 +245,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -248,9 +328,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -288,7 +368,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -394,7 +474,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -536,7 +616,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -544,115 +624,220 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1694FD-E5F2-48E0-A46B-30A7DC8486FF}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{42f063bf-ce3a-473c-8609-3866002c85b0}" enabled="1" method="Standard" siteId="{b914a242-e718-443b-a47c-6b4c649d8c0a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>